--- a/data.xlsx
+++ b/data.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>region</t>
   </si>
@@ -113,13 +113,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +133,19 @@
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -278,7 +292,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,12 +301,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -478,12 +486,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -604,152 +627,161 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1283,8 +1315,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="4" max="5" width="9.875"/>
+  </cols>
   <sheetData>
     <row r="1" ht="40.5" spans="1:18">
       <c r="A1" s="1" t="s">
@@ -2492,36 +2527,38 @@
     </row>
     <row r="30" ht="16.5" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2">
         <v>2026</v>
       </c>
       <c r="C30" s="2">
-        <v>35</v>
-      </c>
-      <c r="D30" s="3">
-        <v>46257</v>
-      </c>
-      <c r="E30" s="3">
-        <v>46263</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1.33</v>
+        <v>39</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="5">
+        <v>12.12</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="4">
-        <v>0.123</v>
-      </c>
-      <c r="J30" s="2">
-        <v>12.3</v>
-      </c>
-      <c r="K30" s="2"/>
+      <c r="I30" s="6">
+        <v>0.259</v>
+      </c>
+      <c r="J30" s="7">
+        <v>52</v>
+      </c>
+      <c r="K30" s="7">
+        <v>2</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="N30" s="7">
+        <v>2</v>
+      </c>
+      <c r="O30" s="7">
+        <v>1</v>
+      </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
@@ -2534,28 +2571,26 @@
         <v>2026</v>
       </c>
       <c r="C31" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31" s="3">
-        <v>46264</v>
+        <v>46257</v>
       </c>
       <c r="E31" s="3">
-        <v>46270</v>
+        <v>46263</v>
       </c>
       <c r="F31" s="2">
-        <v>2.53</v>
+        <v>1.33</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="4">
-        <v>0.163</v>
+        <v>0.123</v>
       </c>
       <c r="J31" s="2">
-        <v>15.9</v>
-      </c>
-      <c r="K31" s="2">
-        <v>0.2</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -2572,24 +2607,24 @@
         <v>2026</v>
       </c>
       <c r="C32" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" s="3">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="E32" s="3">
-        <v>46277</v>
+        <v>46270</v>
       </c>
       <c r="F32" s="2">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="4">
-        <v>0.246</v>
+        <v>0.163</v>
       </c>
       <c r="J32" s="2">
-        <v>24.2</v>
+        <v>15.9</v>
       </c>
       <c r="K32" s="2">
         <v>0.2</v>
@@ -2610,26 +2645,28 @@
         <v>2026</v>
       </c>
       <c r="C33" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" s="3">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="E33" s="3">
-        <v>46284</v>
+        <v>46277</v>
       </c>
       <c r="F33" s="2">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="4">
-        <v>0.207</v>
+        <v>0.246</v>
       </c>
       <c r="J33" s="2">
-        <v>20.7</v>
-      </c>
-      <c r="K33" s="2"/>
+        <v>24.2</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0.2</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -2646,28 +2683,26 @@
         <v>2026</v>
       </c>
       <c r="C34" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" s="3">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="E34" s="3">
-        <v>46291</v>
+        <v>46284</v>
       </c>
       <c r="F34" s="2">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="4">
-        <v>0.263</v>
+        <v>0.207</v>
       </c>
       <c r="J34" s="2">
-        <v>26.1</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0.3</v>
-      </c>
+        <v>20.7</v>
+      </c>
+      <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -2684,24 +2719,24 @@
         <v>2026</v>
       </c>
       <c r="C35" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35" s="3">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="E35" s="3">
-        <v>46298</v>
+        <v>46291</v>
       </c>
       <c r="F35" s="2">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="4">
-        <v>0.28</v>
+        <v>0.263</v>
       </c>
       <c r="J35" s="2">
-        <v>27.8</v>
+        <v>26.1</v>
       </c>
       <c r="K35" s="2">
         <v>0.3</v>
@@ -2716,37 +2751,41 @@
     </row>
     <row r="36" ht="16.5" spans="1:18">
       <c r="A36" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="2">
         <v>2026</v>
       </c>
       <c r="C36" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D36" s="3">
-        <v>46258</v>
+        <v>46292</v>
       </c>
       <c r="E36" s="3">
-        <v>46264</v>
-      </c>
-      <c r="F36" s="2"/>
+        <v>46298</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2.36</v>
+      </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
+      <c r="I36" s="4">
+        <v>0.28</v>
+      </c>
+      <c r="J36" s="2">
+        <v>27.8</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0.3</v>
+      </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
-      <c r="Q36" s="2">
-        <v>6543</v>
-      </c>
-      <c r="R36" s="2">
-        <v>1.76</v>
-      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
     </row>
     <row r="37" ht="16.5" spans="1:18">
       <c r="A37" s="2" t="s">
@@ -2756,13 +2795,13 @@
         <v>2026</v>
       </c>
       <c r="C37" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D37" s="3">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="E37" s="3">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -2776,10 +2815,10 @@
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2">
-        <v>12299</v>
+        <v>6543</v>
       </c>
       <c r="R37" s="2">
-        <v>3.29</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:18">
@@ -2790,13 +2829,13 @@
         <v>2026</v>
       </c>
       <c r="C38" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D38" s="3">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="E38" s="3">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -2810,10 +2849,10 @@
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2">
-        <v>20697</v>
+        <v>12299</v>
       </c>
       <c r="R38" s="2">
-        <v>5.54</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:18">
@@ -2824,13 +2863,13 @@
         <v>2026</v>
       </c>
       <c r="C39" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="3">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="E39" s="3">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -2844,10 +2883,10 @@
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2">
-        <v>31428</v>
+        <v>20697</v>
       </c>
       <c r="R39" s="2">
-        <v>8.48</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:18">
@@ -2858,13 +2897,13 @@
         <v>2026</v>
       </c>
       <c r="C40" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D40" s="3">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="E40" s="3">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -2878,10 +2917,78 @@
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2">
+        <v>31428</v>
+      </c>
+      <c r="R40" s="2">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:18">
+      <c r="A41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C41" s="2">
+        <v>39</v>
+      </c>
+      <c r="D41" s="3">
+        <v>46286</v>
+      </c>
+      <c r="E41" s="3">
+        <v>46292</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2">
         <v>26678</v>
       </c>
-      <c r="R40" s="2">
+      <c r="R41" s="2">
         <v>7.17</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:18">
+      <c r="A42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C42" s="2">
+        <v>40</v>
+      </c>
+      <c r="D42" s="8">
+        <v>46293</v>
+      </c>
+      <c r="E42" s="8">
+        <v>46299</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="10">
+        <v>42320</v>
+      </c>
+      <c r="R42" s="11">
+        <v>11.35</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12240"/>
+    <workbookView windowWidth="24045" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>region</t>
   </si>
@@ -113,14 +113,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,16 +137,29 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial-BoldMT"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -608,7 +622,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -627,137 +641,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -773,17 +788,57 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -833,6 +888,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1315,10 +1371,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="4" max="5" width="9.875"/>
+    <col min="4" max="4" width="13.375" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="40.5" spans="1:18">
@@ -1631,42 +1688,39 @@
     </row>
     <row r="8" ht="16.5" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
         <v>2026</v>
       </c>
       <c r="C8" s="2">
-        <v>35</v>
-      </c>
-      <c r="D8" s="3">
-        <v>46258</v>
-      </c>
-      <c r="E8" s="3">
-        <v>46264</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0.027</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="4">
-        <v>0.019</v>
-      </c>
-      <c r="J8" s="2">
-        <v>7</v>
-      </c>
-      <c r="K8" s="2">
-        <v>33</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2">
-        <v>20</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46300</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46306</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0.046</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.194</v>
+      </c>
+      <c r="J8" s="8">
+        <v>185</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1192</v>
+      </c>
+      <c r="M8" s="8">
+        <v>677</v>
+      </c>
       <c r="O8" s="2"/>
-      <c r="P8" s="2">
-        <v>60</v>
+      <c r="P8" s="9">
+        <f>SUM(J8:M8)</f>
+        <v>2054</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -1679,36 +1733,36 @@
         <v>2026</v>
       </c>
       <c r="C9" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" s="3">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="E9" s="3">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="F9" s="4">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="4">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="J9" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -1721,36 +1775,36 @@
         <v>2026</v>
       </c>
       <c r="C10" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="E10" s="3">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="F10" s="4">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="4">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -1763,36 +1817,36 @@
         <v>2026</v>
       </c>
       <c r="C11" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="E11" s="3">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="F11" s="4">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="4">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="J11" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -1805,36 +1859,36 @@
         <v>2026</v>
       </c>
       <c r="C12" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="E12" s="3">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="F12" s="4">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="4">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="J12" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -1847,117 +1901,119 @@
         <v>2026</v>
       </c>
       <c r="C13" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="3">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="E13" s="3">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="F13" s="4">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="4">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="J13" s="2">
+        <v>15</v>
+      </c>
+      <c r="K13" s="2">
         <v>35</v>
-      </c>
-      <c r="K13" s="2">
-        <v>86</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
     <row r="14" ht="16.5" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
         <v>2026</v>
       </c>
       <c r="C14" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3">
-        <v>46257</v>
+        <v>46293</v>
       </c>
       <c r="E14" s="3">
-        <v>46263</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1.24</v>
+        <v>46299</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.031</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="4">
-        <v>0.1117</v>
+        <v>0.022</v>
       </c>
       <c r="J14" s="2">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="K14" s="2">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2">
-        <v>5</v>
-      </c>
+      <c r="M14" s="2">
+        <v>49</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
+      <c r="P14" s="2">
+        <v>170</v>
+      </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
     <row r="15" ht="16.5" spans="1:18">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2">
         <v>2026</v>
       </c>
       <c r="C15" s="2">
-        <v>36</v>
-      </c>
-      <c r="D15" s="3">
-        <v>46264</v>
-      </c>
-      <c r="E15" s="3">
-        <v>46270</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="G15" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46300</v>
+      </c>
+      <c r="E15" s="6">
+        <v>46306</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.03</v>
+      </c>
       <c r="H15" s="2"/>
-      <c r="I15" s="4">
-        <v>0.1305</v>
-      </c>
-      <c r="J15" s="2">
-        <v>82</v>
-      </c>
-      <c r="K15" s="2">
-        <v>14</v>
-      </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2">
-        <v>4</v>
+      <c r="I15" s="10">
+        <v>0.031</v>
+      </c>
+      <c r="J15" s="11">
+        <v>77</v>
+      </c>
+      <c r="K15" s="11">
+        <v>136</v>
+      </c>
+      <c r="M15" s="11">
+        <v>76</v>
       </c>
       <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
+      <c r="P15" s="9">
+        <f>SUM(J15:M15)</f>
+        <v>289</v>
+      </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
@@ -1969,27 +2025,27 @@
         <v>2026</v>
       </c>
       <c r="C16" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3">
-        <v>46271</v>
+        <v>46257</v>
       </c>
       <c r="E16" s="3">
-        <v>46277</v>
+        <v>46263</v>
       </c>
       <c r="F16" s="2">
-        <v>0.87</v>
+        <v>1.24</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="4">
-        <v>0.1266</v>
+        <v>0.1117</v>
       </c>
       <c r="J16" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K16" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -2009,32 +2065,32 @@
         <v>2026</v>
       </c>
       <c r="C17" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3">
-        <v>46278</v>
+        <v>46264</v>
       </c>
       <c r="E17" s="3">
-        <v>46284</v>
+        <v>46270</v>
       </c>
       <c r="F17" s="2">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="4">
-        <v>0.1065</v>
+        <v>0.1305</v>
       </c>
       <c r="J17" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K17" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -2049,32 +2105,32 @@
         <v>2026</v>
       </c>
       <c r="C18" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" s="3">
-        <v>46285</v>
+        <v>46271</v>
       </c>
       <c r="E18" s="3">
-        <v>46291</v>
+        <v>46277</v>
       </c>
       <c r="F18" s="2">
-        <v>1.06</v>
+        <v>0.87</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="4">
-        <v>0.1153</v>
+        <v>0.1266</v>
       </c>
       <c r="J18" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K18" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -2089,32 +2145,32 @@
         <v>2026</v>
       </c>
       <c r="C19" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" s="3">
-        <v>46292</v>
+        <v>46278</v>
       </c>
       <c r="E19" s="3">
-        <v>46298</v>
+        <v>46284</v>
       </c>
       <c r="F19" s="2">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="4">
-        <v>0.1161</v>
+        <v>0.1065</v>
       </c>
       <c r="J19" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K19" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -2123,40 +2179,38 @@
     </row>
     <row r="20" ht="16.5" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2">
         <v>2026</v>
       </c>
       <c r="C20" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D20" s="3">
-        <v>46263</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="H20" s="2">
-        <v>22.5</v>
-      </c>
+        <v>46285</v>
+      </c>
+      <c r="E20" s="3">
+        <v>46291</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1.06</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
       <c r="I20" s="4">
-        <v>0.131</v>
+        <v>0.1153</v>
       </c>
       <c r="J20" s="2">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="K20" s="2">
-        <v>37.4</v>
-      </c>
-      <c r="L20" s="2">
-        <v>18.8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2">
-        <v>18.8</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -2165,40 +2219,38 @@
     </row>
     <row r="21" ht="16.5" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2">
         <v>2026</v>
       </c>
       <c r="C21" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D21" s="3">
-        <v>46270</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="H21" s="2">
-        <v>23.8</v>
-      </c>
+        <v>46292</v>
+      </c>
+      <c r="E21" s="3">
+        <v>46298</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
       <c r="I21" s="4">
-        <v>0.15</v>
+        <v>0.1161</v>
       </c>
       <c r="J21" s="2">
-        <v>47.1</v>
+        <v>91</v>
       </c>
       <c r="K21" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="L21" s="2">
-        <v>17.6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2">
-        <v>29.4</v>
+        <v>6</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -2207,40 +2259,38 @@
     </row>
     <row r="22" ht="16.5" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2">
         <v>2026</v>
       </c>
-      <c r="C22" s="2">
-        <v>37</v>
-      </c>
-      <c r="D22" s="3">
-        <v>46277</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="H22" s="2">
-        <v>28</v>
-      </c>
-      <c r="I22" s="4">
-        <v>0.214</v>
-      </c>
-      <c r="J22" s="2">
-        <v>37.1</v>
-      </c>
-      <c r="K22" s="2">
-        <v>18.5</v>
-      </c>
-      <c r="L22" s="2">
-        <v>22.2</v>
-      </c>
+      <c r="C22" s="12">
+        <v>41</v>
+      </c>
+      <c r="D22" s="13">
+        <v>46299</v>
+      </c>
+      <c r="E22" s="13">
+        <v>46305</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="15">
+        <v>0.1147</v>
+      </c>
+      <c r="J22" s="16">
+        <v>94</v>
+      </c>
+      <c r="K22" s="16">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2"/>
       <c r="M22" s="2"/>
-      <c r="N22" s="2">
-        <v>22.2</v>
+      <c r="N22" s="16">
+        <v>3</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -2255,34 +2305,34 @@
         <v>2026</v>
       </c>
       <c r="C23" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D23" s="3">
-        <v>46284</v>
+        <v>46263</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2">
-        <v>8.2</v>
+        <v>6.8</v>
       </c>
       <c r="H23" s="2">
-        <v>25.4</v>
+        <v>22.5</v>
       </c>
       <c r="I23" s="4">
-        <v>0.235</v>
+        <v>0.131</v>
       </c>
       <c r="J23" s="2">
-        <v>57.1</v>
+        <v>25</v>
       </c>
       <c r="K23" s="2">
-        <v>17.9</v>
+        <v>37.4</v>
       </c>
       <c r="L23" s="2">
-        <v>10.7</v>
+        <v>18.8</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2">
-        <v>14.3</v>
+        <v>18.8</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -2297,34 +2347,34 @@
         <v>2026</v>
       </c>
       <c r="C24" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D24" s="3">
-        <v>46291</v>
+        <v>46270</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="H24" s="2">
-        <v>27.7</v>
+        <v>23.8</v>
       </c>
       <c r="I24" s="4">
-        <v>0.258</v>
+        <v>0.15</v>
       </c>
       <c r="J24" s="2">
-        <v>57.6</v>
+        <v>47.1</v>
       </c>
       <c r="K24" s="2">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="L24" s="2">
-        <v>15.2</v>
+        <v>17.6</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2">
-        <v>24.2</v>
+        <v>29.4</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -2339,34 +2389,34 @@
         <v>2026</v>
       </c>
       <c r="C25" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D25" s="3">
-        <v>46298</v>
+        <v>46277</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2">
-        <v>8.3</v>
+        <v>8.4</v>
       </c>
       <c r="H25" s="2">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="I25" s="4">
-        <v>0.271</v>
+        <v>0.214</v>
       </c>
       <c r="J25" s="2">
-        <v>76.9</v>
+        <v>37.1</v>
       </c>
       <c r="K25" s="2">
-        <v>7.7</v>
+        <v>18.5</v>
       </c>
       <c r="L25" s="2">
-        <v>15.4</v>
+        <v>22.2</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -2375,152 +2425,168 @@
     </row>
     <row r="26" ht="16.5" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="2">
         <v>2026</v>
       </c>
       <c r="C26" s="2">
-        <v>35</v>
-      </c>
-      <c r="D26" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="D26" s="3">
+        <v>46284</v>
+      </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="2">
-        <v>11.21</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2">
+        <v>8.2</v>
+      </c>
+      <c r="H26" s="2">
+        <v>25.4</v>
+      </c>
       <c r="I26" s="4">
-        <v>0.156</v>
+        <v>0.235</v>
       </c>
       <c r="J26" s="2">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="K26" s="2">
-        <v>6</v>
-      </c>
-      <c r="L26" s="2"/>
+        <v>17.9</v>
+      </c>
+      <c r="L26" s="2">
+        <v>10.7</v>
+      </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2">
-        <v>1</v>
-      </c>
-      <c r="O26" s="2">
-        <v>0</v>
-      </c>
+        <v>14.3</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
     <row r="27" ht="16.5" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="2">
         <v>2026</v>
       </c>
       <c r="C27" s="2">
-        <v>36</v>
-      </c>
-      <c r="D27" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="D27" s="3">
+        <v>46291</v>
+      </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2">
-        <v>12</v>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="H27" s="2">
+        <v>27.7</v>
+      </c>
       <c r="I27" s="4">
-        <v>0.216</v>
+        <v>0.258</v>
       </c>
       <c r="J27" s="2">
-        <v>72</v>
+        <v>57.6</v>
       </c>
       <c r="K27" s="2">
-        <v>8</v>
-      </c>
-      <c r="L27" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="L27" s="2">
+        <v>15.2</v>
+      </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2">
-        <v>0</v>
-      </c>
+        <v>24.2</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
     </row>
     <row r="28" ht="16.5" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" s="2">
         <v>2026</v>
       </c>
       <c r="C28" s="2">
-        <v>37</v>
-      </c>
-      <c r="D28" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="D28" s="3">
+        <v>46298</v>
+      </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2">
-        <v>11.84</v>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2">
+        <v>8.3</v>
+      </c>
+      <c r="H28" s="2">
+        <v>27.9</v>
+      </c>
       <c r="I28" s="4">
-        <v>0.233</v>
+        <v>0.271</v>
       </c>
       <c r="J28" s="2">
-        <v>63</v>
+        <v>76.9</v>
       </c>
       <c r="K28" s="2">
-        <v>1</v>
-      </c>
-      <c r="L28" s="2"/>
+        <v>7.7</v>
+      </c>
+      <c r="L28" s="2">
+        <v>15.4</v>
+      </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2">
-        <v>3</v>
-      </c>
-      <c r="O28" s="2">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
     <row r="29" ht="16.5" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="2">
-        <v>2026</v>
-      </c>
-      <c r="C29" s="2">
-        <v>38</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B29" s="17">
+        <v>2027</v>
+      </c>
+      <c r="C29" s="18">
+        <v>41</v>
+      </c>
+      <c r="D29" s="19">
+        <v>46305</v>
+      </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="2">
-        <v>12.24</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="4">
-        <v>0.239</v>
-      </c>
-      <c r="J29" s="2">
-        <v>58</v>
-      </c>
-      <c r="K29" s="2">
-        <v>2</v>
-      </c>
-      <c r="L29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="8">
+        <v>7.4</v>
+      </c>
+      <c r="H29" s="8">
+        <v>27.1</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="J29" s="16">
+        <v>73.3</v>
+      </c>
+      <c r="K29" s="16">
+        <v>6.7</v>
+      </c>
+      <c r="L29" s="16">
+        <v>6.7</v>
+      </c>
       <c r="M29" s="2"/>
-      <c r="N29" s="2">
-        <v>1</v>
-      </c>
-      <c r="O29" s="2">
-        <v>0</v>
-      </c>
+      <c r="N29" s="16">
+        <v>13.3</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
@@ -2533,31 +2599,31 @@
         <v>2026</v>
       </c>
       <c r="C30" s="2">
-        <v>39</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="5">
-        <v>12.12</v>
+        <v>35</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2">
+        <v>11.21</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="6">
-        <v>0.259</v>
-      </c>
-      <c r="J30" s="7">
-        <v>52</v>
-      </c>
-      <c r="K30" s="7">
-        <v>2</v>
+      <c r="I30" s="4">
+        <v>0.156</v>
+      </c>
+      <c r="J30" s="2">
+        <v>40</v>
+      </c>
+      <c r="K30" s="2">
+        <v>6</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="N30" s="7">
-        <v>2</v>
-      </c>
-      <c r="O30" s="7">
+      <c r="N30" s="2">
         <v>1</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
@@ -2565,148 +2631,152 @@
     </row>
     <row r="31" ht="16.5" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2">
         <v>2026</v>
       </c>
       <c r="C31" s="2">
-        <v>35</v>
-      </c>
-      <c r="D31" s="3">
-        <v>46257</v>
-      </c>
-      <c r="E31" s="3">
-        <v>46263</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
       <c r="F31" s="2">
-        <v>1.33</v>
+        <v>12</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="4">
-        <v>0.123</v>
+        <v>0.216</v>
       </c>
       <c r="J31" s="2">
-        <v>12.3</v>
-      </c>
-      <c r="K31" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="K31" s="2">
+        <v>8</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="N31" s="2">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
     <row r="32" ht="16.5" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="2">
         <v>2026</v>
       </c>
       <c r="C32" s="2">
-        <v>36</v>
-      </c>
-      <c r="D32" s="3">
-        <v>46264</v>
-      </c>
-      <c r="E32" s="3">
-        <v>46270</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
       <c r="F32" s="2">
-        <v>2.53</v>
+        <v>11.84</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="4">
-        <v>0.163</v>
+        <v>0.233</v>
       </c>
       <c r="J32" s="2">
-        <v>15.9</v>
+        <v>63</v>
       </c>
       <c r="K32" s="2">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="N32" s="2">
+        <v>3</v>
+      </c>
+      <c r="O32" s="2">
+        <v>2</v>
+      </c>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
     <row r="33" ht="16.5" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" s="2">
         <v>2026</v>
       </c>
       <c r="C33" s="2">
-        <v>37</v>
-      </c>
-      <c r="D33" s="3">
-        <v>46271</v>
-      </c>
-      <c r="E33" s="3">
-        <v>46277</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
       <c r="F33" s="2">
-        <v>3.1</v>
+        <v>12.24</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="4">
-        <v>0.246</v>
+        <v>0.239</v>
       </c>
       <c r="J33" s="2">
-        <v>24.2</v>
+        <v>58</v>
       </c>
       <c r="K33" s="2">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="N33" s="2">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2">
+        <v>0</v>
+      </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
     <row r="34" ht="16.5" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" s="2">
         <v>2026</v>
       </c>
       <c r="C34" s="2">
-        <v>38</v>
-      </c>
-      <c r="D34" s="3">
-        <v>46278</v>
-      </c>
-      <c r="E34" s="3">
-        <v>46284</v>
-      </c>
-      <c r="F34" s="2">
-        <v>3.23</v>
+        <v>39</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="20">
+        <v>12.12</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="4">
-        <v>0.207</v>
-      </c>
-      <c r="J34" s="2">
-        <v>20.7</v>
-      </c>
-      <c r="K34" s="2"/>
+      <c r="I34" s="21">
+        <v>0.259</v>
+      </c>
+      <c r="J34" s="22">
+        <v>52</v>
+      </c>
+      <c r="K34" s="22">
+        <v>2</v>
+      </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="N34" s="22">
+        <v>2</v>
+      </c>
+      <c r="O34" s="22">
+        <v>1</v>
+      </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
@@ -2719,28 +2789,26 @@
         <v>2026</v>
       </c>
       <c r="C35" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D35" s="3">
-        <v>46285</v>
+        <v>46257</v>
       </c>
       <c r="E35" s="3">
-        <v>46291</v>
+        <v>46263</v>
       </c>
       <c r="F35" s="2">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="4">
-        <v>0.263</v>
+        <v>0.123</v>
       </c>
       <c r="J35" s="2">
-        <v>26.1</v>
-      </c>
-      <c r="K35" s="2">
-        <v>0.3</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -2757,27 +2825,27 @@
         <v>2026</v>
       </c>
       <c r="C36" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D36" s="3">
-        <v>46292</v>
+        <v>46264</v>
       </c>
       <c r="E36" s="3">
-        <v>46298</v>
+        <v>46270</v>
       </c>
       <c r="F36" s="2">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="4">
-        <v>0.28</v>
+        <v>0.163</v>
       </c>
       <c r="J36" s="2">
-        <v>27.8</v>
+        <v>15.9</v>
       </c>
       <c r="K36" s="2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -2789,173 +2857,189 @@
     </row>
     <row r="37" ht="16.5" spans="1:18">
       <c r="A37" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="2">
         <v>2026</v>
       </c>
       <c r="C37" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D37" s="3">
-        <v>46258</v>
+        <v>46271</v>
       </c>
       <c r="E37" s="3">
-        <v>46264</v>
-      </c>
-      <c r="F37" s="2"/>
+        <v>46277</v>
+      </c>
+      <c r="F37" s="2">
+        <v>3.1</v>
+      </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
+      <c r="I37" s="4">
+        <v>0.246</v>
+      </c>
+      <c r="J37" s="2">
+        <v>24.2</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0.2</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
-      <c r="Q37" s="2">
-        <v>6543</v>
-      </c>
-      <c r="R37" s="2">
-        <v>1.76</v>
-      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
     </row>
     <row r="38" ht="16.5" spans="1:18">
       <c r="A38" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="2">
         <v>2026</v>
       </c>
       <c r="C38" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D38" s="3">
-        <v>46265</v>
+        <v>46278</v>
       </c>
       <c r="E38" s="3">
-        <v>46271</v>
-      </c>
-      <c r="F38" s="2"/>
+        <v>46284</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3.23</v>
+      </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
+      <c r="I38" s="4">
+        <v>0.207</v>
+      </c>
+      <c r="J38" s="2">
+        <v>20.7</v>
+      </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
-      <c r="Q38" s="2">
-        <v>12299</v>
-      </c>
-      <c r="R38" s="2">
-        <v>3.29</v>
-      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
     </row>
     <row r="39" ht="16.5" spans="1:18">
       <c r="A39" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="2">
         <v>2026</v>
       </c>
       <c r="C39" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D39" s="3">
-        <v>46272</v>
+        <v>46285</v>
       </c>
       <c r="E39" s="3">
-        <v>46278</v>
-      </c>
-      <c r="F39" s="2"/>
+        <v>46291</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3.3</v>
+      </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
+      <c r="I39" s="4">
+        <v>0.263</v>
+      </c>
+      <c r="J39" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="K39" s="2">
+        <v>0.3</v>
+      </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
-      <c r="Q39" s="2">
-        <v>20697</v>
-      </c>
-      <c r="R39" s="2">
-        <v>5.54</v>
-      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
     </row>
     <row r="40" ht="16.5" spans="1:18">
       <c r="A40" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B40" s="2">
         <v>2026</v>
       </c>
       <c r="C40" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D40" s="3">
-        <v>46279</v>
+        <v>46292</v>
       </c>
       <c r="E40" s="3">
-        <v>46285</v>
-      </c>
-      <c r="F40" s="2"/>
+        <v>46298</v>
+      </c>
+      <c r="F40" s="2">
+        <v>2.36</v>
+      </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
+      <c r="I40" s="4">
+        <v>0.28</v>
+      </c>
+      <c r="J40" s="2">
+        <v>27.8</v>
+      </c>
+      <c r="K40" s="2">
+        <v>0.3</v>
+      </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
-      <c r="Q40" s="2">
-        <v>31428</v>
-      </c>
-      <c r="R40" s="2">
-        <v>8.48</v>
-      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
     </row>
     <row r="41" ht="16.5" spans="1:18">
       <c r="A41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B41" s="2">
         <v>2026</v>
       </c>
-      <c r="C41" s="2">
-        <v>39</v>
-      </c>
-      <c r="D41" s="3">
-        <v>46286</v>
-      </c>
-      <c r="E41" s="3">
-        <v>46292</v>
-      </c>
-      <c r="F41" s="2"/>
+      <c r="C41" s="23">
+        <v>41</v>
+      </c>
+      <c r="D41" s="24">
+        <v>46299</v>
+      </c>
+      <c r="E41" s="24">
+        <v>46305</v>
+      </c>
+      <c r="F41" s="25">
+        <v>2.16</v>
+      </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
+      <c r="I41" s="26">
+        <v>0.252</v>
+      </c>
+      <c r="J41" s="27">
+        <v>25.2</v>
+      </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
-      <c r="Q41" s="2">
-        <v>26678</v>
-      </c>
-      <c r="R41" s="2">
-        <v>7.17</v>
-      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
     </row>
     <row r="42" ht="16.5" spans="1:18">
       <c r="A42" s="2" t="s">
@@ -2965,30 +3049,223 @@
         <v>2026</v>
       </c>
       <c r="C42" s="2">
+        <v>35</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46258</v>
+      </c>
+      <c r="E42" s="3">
+        <v>46264</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2">
+        <v>6543</v>
+      </c>
+      <c r="R42" s="2">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:18">
+      <c r="A43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C43" s="2">
+        <v>36</v>
+      </c>
+      <c r="D43" s="3">
+        <v>46265</v>
+      </c>
+      <c r="E43" s="3">
+        <v>46271</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2">
+        <v>12299</v>
+      </c>
+      <c r="R43" s="2">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:18">
+      <c r="A44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C44" s="2">
+        <v>37</v>
+      </c>
+      <c r="D44" s="3">
+        <v>46272</v>
+      </c>
+      <c r="E44" s="3">
+        <v>46278</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2">
+        <v>20697</v>
+      </c>
+      <c r="R44" s="2">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:18">
+      <c r="A45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C45" s="2">
+        <v>38</v>
+      </c>
+      <c r="D45" s="3">
+        <v>46279</v>
+      </c>
+      <c r="E45" s="3">
+        <v>46285</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2">
+        <v>31428</v>
+      </c>
+      <c r="R45" s="2">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:18">
+      <c r="A46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C46" s="2">
+        <v>39</v>
+      </c>
+      <c r="D46" s="3">
+        <v>46286</v>
+      </c>
+      <c r="E46" s="3">
+        <v>46292</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2">
+        <v>26678</v>
+      </c>
+      <c r="R46" s="2">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:18">
+      <c r="A47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C47" s="2">
         <v>40</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D47" s="28">
         <v>46293</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E47" s="28">
         <v>46299</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="10">
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="30">
         <v>42320</v>
       </c>
-      <c r="R42" s="11">
+      <c r="R47" s="31">
         <v>11.35</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:18">
+      <c r="A48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C48" s="2">
+        <v>41</v>
+      </c>
+      <c r="D48" s="32">
+        <v>46300</v>
+      </c>
+      <c r="E48" s="32">
+        <v>46306</v>
+      </c>
+      <c r="Q48" s="33">
+        <v>47746</v>
+      </c>
+      <c r="R48" s="8">
+        <v>12.81</v>
       </c>
     </row>
   </sheetData>
